--- a/public/templates/rnkgrade.xlsx
+++ b/public/templates/rnkgrade.xlsx
@@ -1,25 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\saat2024\public\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\saat\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{463BC102-20EF-4E38-81D6-0FCC7440430C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="4515"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Central" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Nº</t>
   </si>
@@ -66,13 +81,16 @@
     <t>T3</t>
   </si>
   <si>
-    <t>GESTIÓN 2024 RANKING OFICIAL</t>
+    <t>RANKING OFICIAL</t>
+  </si>
+  <si>
+    <t>CURSO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#.00"/>
     <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
@@ -392,7 +410,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="41">
+  <borders count="45">
     <border>
       <left/>
       <right/>
@@ -919,6 +937,50 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -1026,84 +1088,101 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="27" fillId="23" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="27" fillId="23" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="27" fillId="23" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="27" fillId="23" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="27" fillId="23" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="27" fillId="23" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="62" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="62" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="62" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="23" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1132,115 +1211,136 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="62" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="62" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="62" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="26" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="27" fillId="23" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="27" fillId="23" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="27" fillId="23" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="27" fillId="23" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="27" fillId="23" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="27" fillId="23" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="27" fillId="23" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="27" fillId="23" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="27" fillId="23" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="71">
-    <cellStyle name="20% - Accent1" xfId="1"/>
-    <cellStyle name="20% - Accent1 2" xfId="2"/>
-    <cellStyle name="20% - Accent2" xfId="3"/>
-    <cellStyle name="20% - Accent2 2" xfId="4"/>
-    <cellStyle name="20% - Accent3" xfId="5"/>
-    <cellStyle name="20% - Accent3 2" xfId="6"/>
-    <cellStyle name="20% - Accent4" xfId="7"/>
-    <cellStyle name="20% - Accent4 2" xfId="8"/>
-    <cellStyle name="20% - Accent5" xfId="9"/>
-    <cellStyle name="20% - Accent5 2" xfId="10"/>
-    <cellStyle name="20% - Accent6" xfId="11"/>
-    <cellStyle name="20% - Accent6 2" xfId="12"/>
-    <cellStyle name="40% - Accent1" xfId="13"/>
-    <cellStyle name="40% - Accent1 2" xfId="14"/>
-    <cellStyle name="40% - Accent2" xfId="15"/>
-    <cellStyle name="40% - Accent2 2" xfId="16"/>
-    <cellStyle name="40% - Accent3" xfId="17"/>
-    <cellStyle name="40% - Accent3 2" xfId="18"/>
-    <cellStyle name="40% - Accent4" xfId="19"/>
-    <cellStyle name="40% - Accent4 2" xfId="20"/>
-    <cellStyle name="40% - Accent5" xfId="21"/>
-    <cellStyle name="40% - Accent5 2" xfId="22"/>
-    <cellStyle name="40% - Accent6" xfId="23"/>
-    <cellStyle name="40% - Accent6 2" xfId="24"/>
-    <cellStyle name="60% - Accent1" xfId="25"/>
-    <cellStyle name="60% - Accent2" xfId="26"/>
-    <cellStyle name="60% - Accent3" xfId="27"/>
-    <cellStyle name="60% - Accent4" xfId="28"/>
-    <cellStyle name="60% - Accent5" xfId="29"/>
-    <cellStyle name="60% - Accent6" xfId="30"/>
-    <cellStyle name="Accent1" xfId="31"/>
-    <cellStyle name="Accent2" xfId="32"/>
-    <cellStyle name="Accent3" xfId="33"/>
-    <cellStyle name="Accent4" xfId="34"/>
-    <cellStyle name="Accent5" xfId="35"/>
-    <cellStyle name="Accent6" xfId="36"/>
-    <cellStyle name="Bad" xfId="37"/>
-    <cellStyle name="Calculation" xfId="38"/>
-    <cellStyle name="Check Cell" xfId="39"/>
-    <cellStyle name="Comma" xfId="40"/>
-    <cellStyle name="Currency" xfId="41"/>
-    <cellStyle name="Date" xfId="42"/>
-    <cellStyle name="Explanatory Text" xfId="43"/>
-    <cellStyle name="F2" xfId="44"/>
-    <cellStyle name="F3" xfId="45"/>
-    <cellStyle name="F4" xfId="46"/>
-    <cellStyle name="F5" xfId="47"/>
-    <cellStyle name="F6" xfId="48"/>
-    <cellStyle name="F7" xfId="49"/>
-    <cellStyle name="F8" xfId="50"/>
-    <cellStyle name="Fixed" xfId="51"/>
-    <cellStyle name="Good" xfId="52"/>
-    <cellStyle name="Heading 1" xfId="53"/>
-    <cellStyle name="Heading 2" xfId="54"/>
-    <cellStyle name="Heading 3" xfId="55"/>
-    <cellStyle name="Heading 4" xfId="56"/>
-    <cellStyle name="Heading1" xfId="57"/>
-    <cellStyle name="Heading2" xfId="58"/>
-    <cellStyle name="Input" xfId="59"/>
-    <cellStyle name="Linked Cell" xfId="60"/>
+    <cellStyle name="20% - Accent1" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="20% - Accent1 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="20% - Accent2" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="20% - Accent2 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="20% - Accent3" xfId="5" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="20% - Accent3 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="20% - Accent4" xfId="7" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="20% - Accent4 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="20% - Accent5" xfId="9" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="20% - Accent5 2" xfId="10" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="20% - Accent6" xfId="11" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="20% - Accent6 2" xfId="12" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="40% - Accent1" xfId="13" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="40% - Accent1 2" xfId="14" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="40% - Accent2" xfId="15" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="40% - Accent2 2" xfId="16" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="40% - Accent3" xfId="17" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="40% - Accent3 2" xfId="18" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="40% - Accent4" xfId="19" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
+    <cellStyle name="40% - Accent4 2" xfId="20" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="40% - Accent5" xfId="21" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
+    <cellStyle name="40% - Accent5 2" xfId="22" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
+    <cellStyle name="40% - Accent6" xfId="23" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
+    <cellStyle name="40% - Accent6 2" xfId="24" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
+    <cellStyle name="60% - Accent1" xfId="25" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
+    <cellStyle name="60% - Accent2" xfId="26" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
+    <cellStyle name="60% - Accent3" xfId="27" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
+    <cellStyle name="60% - Accent4" xfId="28" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
+    <cellStyle name="60% - Accent5" xfId="29" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
+    <cellStyle name="60% - Accent6" xfId="30" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
+    <cellStyle name="Accent1" xfId="31" xr:uid="{00000000-0005-0000-0000-00001E000000}"/>
+    <cellStyle name="Accent2" xfId="32" xr:uid="{00000000-0005-0000-0000-00001F000000}"/>
+    <cellStyle name="Accent3" xfId="33" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
+    <cellStyle name="Accent4" xfId="34" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
+    <cellStyle name="Accent5" xfId="35" xr:uid="{00000000-0005-0000-0000-000022000000}"/>
+    <cellStyle name="Accent6" xfId="36" xr:uid="{00000000-0005-0000-0000-000023000000}"/>
+    <cellStyle name="Bad" xfId="37" xr:uid="{00000000-0005-0000-0000-000024000000}"/>
+    <cellStyle name="Calculation" xfId="38" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
+    <cellStyle name="Check Cell" xfId="39" xr:uid="{00000000-0005-0000-0000-000026000000}"/>
+    <cellStyle name="Comma" xfId="40" xr:uid="{00000000-0005-0000-0000-000027000000}"/>
+    <cellStyle name="Currency" xfId="41" xr:uid="{00000000-0005-0000-0000-000028000000}"/>
+    <cellStyle name="Date" xfId="42" xr:uid="{00000000-0005-0000-0000-000029000000}"/>
+    <cellStyle name="Explanatory Text" xfId="43" xr:uid="{00000000-0005-0000-0000-00002A000000}"/>
+    <cellStyle name="F2" xfId="44" xr:uid="{00000000-0005-0000-0000-00002B000000}"/>
+    <cellStyle name="F3" xfId="45" xr:uid="{00000000-0005-0000-0000-00002C000000}"/>
+    <cellStyle name="F4" xfId="46" xr:uid="{00000000-0005-0000-0000-00002D000000}"/>
+    <cellStyle name="F5" xfId="47" xr:uid="{00000000-0005-0000-0000-00002E000000}"/>
+    <cellStyle name="F6" xfId="48" xr:uid="{00000000-0005-0000-0000-00002F000000}"/>
+    <cellStyle name="F7" xfId="49" xr:uid="{00000000-0005-0000-0000-000030000000}"/>
+    <cellStyle name="F8" xfId="50" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="Fixed" xfId="51" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="Good" xfId="52" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
+    <cellStyle name="Heading 1" xfId="53" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
+    <cellStyle name="Heading 2" xfId="54" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
+    <cellStyle name="Heading 3" xfId="55" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
+    <cellStyle name="Heading 4" xfId="56" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
+    <cellStyle name="Heading1" xfId="57" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
+    <cellStyle name="Heading2" xfId="58" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
+    <cellStyle name="Input" xfId="59" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
+    <cellStyle name="Linked Cell" xfId="60" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="61"/>
-    <cellStyle name="Normal_TRIM3y4" xfId="62"/>
-    <cellStyle name="Note" xfId="63"/>
-    <cellStyle name="Note 2" xfId="64"/>
-    <cellStyle name="Output" xfId="65"/>
-    <cellStyle name="Percent" xfId="66"/>
-    <cellStyle name="Porcentaje 2" xfId="67"/>
-    <cellStyle name="Porcentaje 3" xfId="68"/>
-    <cellStyle name="Title" xfId="69"/>
-    <cellStyle name="Warning Text" xfId="70"/>
+    <cellStyle name="Normal 2" xfId="61" xr:uid="{00000000-0005-0000-0000-00003D000000}"/>
+    <cellStyle name="Normal_TRIM3y4" xfId="62" xr:uid="{00000000-0005-0000-0000-00003E000000}"/>
+    <cellStyle name="Note" xfId="63" xr:uid="{00000000-0005-0000-0000-00003F000000}"/>
+    <cellStyle name="Note 2" xfId="64" xr:uid="{00000000-0005-0000-0000-000040000000}"/>
+    <cellStyle name="Output" xfId="65" xr:uid="{00000000-0005-0000-0000-000041000000}"/>
+    <cellStyle name="Percent" xfId="66" xr:uid="{00000000-0005-0000-0000-000042000000}"/>
+    <cellStyle name="Porcentaje 2" xfId="67" xr:uid="{00000000-0005-0000-0000-000043000000}"/>
+    <cellStyle name="Porcentaje 3" xfId="68" xr:uid="{00000000-0005-0000-0000-000044000000}"/>
+    <cellStyle name="Title" xfId="69" xr:uid="{00000000-0005-0000-0000-000045000000}"/>
+    <cellStyle name="Warning Text" xfId="70" xr:uid="{00000000-0005-0000-0000-000046000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1260,67 +1360,48 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>133350</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1019175</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:colOff>1114425</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>68438</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1057" name="1 Imagen"/>
+        <xdr:cNvPr id="5" name="Imagen 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{349DAE93-9DEF-4160-AB08-FFADD7D1C109}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
           </a:extLst>
         </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
+        <a:srcRect l="7383" t="8405"/>
+        <a:stretch/>
       </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
+      <xdr:spPr>
         <a:xfrm>
-          <a:off x="133350" y="28575"/>
-          <a:ext cx="1085850" cy="657225"/>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1314450" cy="830438"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -1404,6 +1485,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -1439,6 +1537,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1614,78 +1729,85 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:O103"/>
+  <dimension ref="A2:P103"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="45.85546875" customWidth="1"/>
-    <col min="3" max="5" width="9.7109375" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="9.7109375" customWidth="1"/>
-    <col min="8" max="21" width="3.85546875" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" customWidth="1"/>
+    <col min="4" max="6" width="9.7109375" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" customWidth="1"/>
+    <col min="9" max="22" width="3.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="39" t="s">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="40" t="s">
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="41" t="s">
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-    </row>
-    <row r="5" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="42"/>
-      <c r="B5" s="42"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="47" t="s">
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+    </row>
+    <row r="5" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="24"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="49" t="s">
+      <c r="B6" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="43" t="s">
+      <c r="C6" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="46"/>
-      <c r="H6" s="1"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="28"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
@@ -1693,1146 +1815,1248 @@
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="48"/>
-      <c r="B7" s="50"/>
-      <c r="C7" s="9" t="s">
+      <c r="P6" s="1"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="30"/>
+      <c r="B7" s="32"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="E7" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="F7" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="25"/>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="15"/>
+      <c r="H7" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="18">
         <v>1</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="21"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="7">
+      <c r="B8" s="45"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="53"/>
+      <c r="F8" s="53"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="12"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="19">
         <v>2</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="21"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
+      <c r="B9" s="47"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="52"/>
+      <c r="E9" s="53"/>
+      <c r="F9" s="53"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="12"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="19">
         <v>3</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="21"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="29">
+      <c r="B10" s="47"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="52"/>
+      <c r="E10" s="53"/>
+      <c r="F10" s="53"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="12"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="19">
         <v>4</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="21"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="29">
+      <c r="B11" s="47"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="53"/>
+      <c r="F11" s="53"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="12"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="19">
         <v>5</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="21"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="29">
+      <c r="B12" s="47"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="53"/>
+      <c r="F12" s="53"/>
+      <c r="G12" s="54"/>
+      <c r="H12" s="12"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="19">
         <v>6</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="22"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="29">
+      <c r="B13" s="47"/>
+      <c r="C13" s="46"/>
+      <c r="D13" s="55"/>
+      <c r="E13" s="56"/>
+      <c r="F13" s="56"/>
+      <c r="G13" s="57"/>
+      <c r="H13" s="13"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="19">
         <v>7</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="21"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="29">
+      <c r="B14" s="47"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="52"/>
+      <c r="E14" s="53"/>
+      <c r="F14" s="53"/>
+      <c r="G14" s="54"/>
+      <c r="H14" s="12"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" s="19">
         <v>8</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="21"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="29">
+      <c r="B15" s="47"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="54"/>
+      <c r="H15" s="12"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" s="19">
         <v>9</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="26"/>
-      <c r="G16" s="21"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="29">
+      <c r="B16" s="47"/>
+      <c r="C16" s="48"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="53"/>
+      <c r="F16" s="53"/>
+      <c r="G16" s="54"/>
+      <c r="H16" s="12"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="19">
         <v>10</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="21"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="29">
+      <c r="B17" s="47"/>
+      <c r="C17" s="48"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="53"/>
+      <c r="F17" s="53"/>
+      <c r="G17" s="54"/>
+      <c r="H17" s="12"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="19">
         <v>11</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="22"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="29">
+      <c r="B18" s="47"/>
+      <c r="C18" s="46"/>
+      <c r="D18" s="55"/>
+      <c r="E18" s="56"/>
+      <c r="F18" s="56"/>
+      <c r="G18" s="57"/>
+      <c r="H18" s="13"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="19">
         <v>12</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="21"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="29">
+      <c r="B19" s="47"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="52"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="53"/>
+      <c r="G19" s="54"/>
+      <c r="H19" s="12"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="19">
         <v>13</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="21"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="29">
+      <c r="B20" s="47"/>
+      <c r="C20" s="48"/>
+      <c r="D20" s="52"/>
+      <c r="E20" s="53"/>
+      <c r="F20" s="53"/>
+      <c r="G20" s="54"/>
+      <c r="H20" s="12"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="19">
         <v>14</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="21"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="29">
+      <c r="B21" s="47"/>
+      <c r="C21" s="48"/>
+      <c r="D21" s="52"/>
+      <c r="E21" s="53"/>
+      <c r="F21" s="53"/>
+      <c r="G21" s="54"/>
+      <c r="H21" s="12"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="19">
         <v>15</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="26"/>
-      <c r="G22" s="21"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="29">
+      <c r="B22" s="47"/>
+      <c r="C22" s="48"/>
+      <c r="D22" s="52"/>
+      <c r="E22" s="53"/>
+      <c r="F22" s="53"/>
+      <c r="G22" s="54"/>
+      <c r="H22" s="12"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="19">
         <v>16</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="22"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="29">
+      <c r="B23" s="47"/>
+      <c r="C23" s="46"/>
+      <c r="D23" s="55"/>
+      <c r="E23" s="56"/>
+      <c r="F23" s="56"/>
+      <c r="G23" s="57"/>
+      <c r="H23" s="13"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="19">
         <v>17</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="21"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="29">
+      <c r="B24" s="47"/>
+      <c r="C24" s="48"/>
+      <c r="D24" s="52"/>
+      <c r="E24" s="53"/>
+      <c r="F24" s="53"/>
+      <c r="G24" s="54"/>
+      <c r="H24" s="12"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="19">
         <v>18</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="21"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="29">
+      <c r="B25" s="47"/>
+      <c r="C25" s="48"/>
+      <c r="D25" s="52"/>
+      <c r="E25" s="53"/>
+      <c r="F25" s="53"/>
+      <c r="G25" s="54"/>
+      <c r="H25" s="12"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="19">
         <v>19</v>
       </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="21"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="29">
+      <c r="B26" s="47"/>
+      <c r="C26" s="48"/>
+      <c r="D26" s="52"/>
+      <c r="E26" s="53"/>
+      <c r="F26" s="53"/>
+      <c r="G26" s="54"/>
+      <c r="H26" s="12"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="19">
         <v>20</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="21"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="29">
+      <c r="B27" s="47"/>
+      <c r="C27" s="48"/>
+      <c r="D27" s="52"/>
+      <c r="E27" s="53"/>
+      <c r="F27" s="53"/>
+      <c r="G27" s="54"/>
+      <c r="H27" s="12"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="19">
         <v>21</v>
       </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="26"/>
-      <c r="G28" s="21"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="29">
+      <c r="B28" s="47"/>
+      <c r="C28" s="48"/>
+      <c r="D28" s="52"/>
+      <c r="E28" s="53"/>
+      <c r="F28" s="53"/>
+      <c r="G28" s="54"/>
+      <c r="H28" s="12"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="19">
         <v>22</v>
       </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="22"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="29">
+      <c r="B29" s="47"/>
+      <c r="C29" s="46"/>
+      <c r="D29" s="55"/>
+      <c r="E29" s="56"/>
+      <c r="F29" s="56"/>
+      <c r="G29" s="57"/>
+      <c r="H29" s="13"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="19">
         <v>23</v>
       </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="26"/>
-      <c r="G30" s="21"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="29">
+      <c r="B30" s="47"/>
+      <c r="C30" s="48"/>
+      <c r="D30" s="52"/>
+      <c r="E30" s="53"/>
+      <c r="F30" s="53"/>
+      <c r="G30" s="54"/>
+      <c r="H30" s="12"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="19">
         <v>24</v>
       </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="26"/>
-      <c r="G31" s="21"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="29">
+      <c r="B31" s="47"/>
+      <c r="C31" s="48"/>
+      <c r="D31" s="52"/>
+      <c r="E31" s="53"/>
+      <c r="F31" s="53"/>
+      <c r="G31" s="54"/>
+      <c r="H31" s="12"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="19">
         <v>25</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="26"/>
-      <c r="G32" s="21"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="29">
+      <c r="B32" s="47"/>
+      <c r="C32" s="48"/>
+      <c r="D32" s="52"/>
+      <c r="E32" s="53"/>
+      <c r="F32" s="53"/>
+      <c r="G32" s="54"/>
+      <c r="H32" s="12"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="19">
         <v>26</v>
       </c>
-      <c r="B33" s="3"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="21"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="29">
+      <c r="B33" s="47"/>
+      <c r="C33" s="48"/>
+      <c r="D33" s="52"/>
+      <c r="E33" s="53"/>
+      <c r="F33" s="53"/>
+      <c r="G33" s="54"/>
+      <c r="H33" s="12"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="19">
         <v>27</v>
       </c>
-      <c r="B34" s="3"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="27"/>
-      <c r="G34" s="22"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="29">
+      <c r="B34" s="47"/>
+      <c r="C34" s="46"/>
+      <c r="D34" s="55"/>
+      <c r="E34" s="56"/>
+      <c r="F34" s="56"/>
+      <c r="G34" s="57"/>
+      <c r="H34" s="13"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="19">
         <v>28</v>
       </c>
-      <c r="B35" s="3"/>
-      <c r="C35" s="12"/>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="26"/>
-      <c r="G35" s="21"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="29">
+      <c r="B35" s="47"/>
+      <c r="C35" s="48"/>
+      <c r="D35" s="52"/>
+      <c r="E35" s="53"/>
+      <c r="F35" s="53"/>
+      <c r="G35" s="54"/>
+      <c r="H35" s="12"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="19">
         <v>29</v>
       </c>
-      <c r="B36" s="3"/>
-      <c r="C36" s="12"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="26"/>
-      <c r="G36" s="21"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="29">
+      <c r="B36" s="47"/>
+      <c r="C36" s="48"/>
+      <c r="D36" s="52"/>
+      <c r="E36" s="53"/>
+      <c r="F36" s="53"/>
+      <c r="G36" s="54"/>
+      <c r="H36" s="12"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="19">
         <v>30</v>
       </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="12"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="26"/>
-      <c r="G37" s="21"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="29">
+      <c r="B37" s="47"/>
+      <c r="C37" s="48"/>
+      <c r="D37" s="52"/>
+      <c r="E37" s="53"/>
+      <c r="F37" s="53"/>
+      <c r="G37" s="54"/>
+      <c r="H37" s="12"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="19">
         <v>31</v>
       </c>
-      <c r="B38" s="3"/>
-      <c r="C38" s="12"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="26"/>
-      <c r="G38" s="21"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="29">
+      <c r="B38" s="47"/>
+      <c r="C38" s="48"/>
+      <c r="D38" s="52"/>
+      <c r="E38" s="53"/>
+      <c r="F38" s="53"/>
+      <c r="G38" s="54"/>
+      <c r="H38" s="12"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="19">
         <v>32</v>
       </c>
-      <c r="B39" s="3"/>
-      <c r="C39" s="12"/>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="26"/>
-      <c r="G39" s="21"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="29">
+      <c r="B39" s="47"/>
+      <c r="C39" s="48"/>
+      <c r="D39" s="52"/>
+      <c r="E39" s="53"/>
+      <c r="F39" s="53"/>
+      <c r="G39" s="54"/>
+      <c r="H39" s="12"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="19">
         <v>33</v>
       </c>
-      <c r="B40" s="3"/>
-      <c r="C40" s="15"/>
-      <c r="D40" s="16"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="27"/>
-      <c r="G40" s="22"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="29">
+      <c r="B40" s="47"/>
+      <c r="C40" s="46"/>
+      <c r="D40" s="55"/>
+      <c r="E40" s="56"/>
+      <c r="F40" s="56"/>
+      <c r="G40" s="57"/>
+      <c r="H40" s="13"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="19">
         <v>34</v>
       </c>
-      <c r="B41" s="3"/>
-      <c r="C41" s="12"/>
-      <c r="D41" s="13"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="26"/>
-      <c r="G41" s="21"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="29">
+      <c r="B41" s="47"/>
+      <c r="C41" s="48"/>
+      <c r="D41" s="52"/>
+      <c r="E41" s="53"/>
+      <c r="F41" s="53"/>
+      <c r="G41" s="54"/>
+      <c r="H41" s="12"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="19">
         <v>35</v>
       </c>
-      <c r="B42" s="3"/>
-      <c r="C42" s="12"/>
-      <c r="D42" s="13"/>
-      <c r="E42" s="13"/>
-      <c r="F42" s="26"/>
-      <c r="G42" s="21"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="29">
+      <c r="B42" s="47"/>
+      <c r="C42" s="48"/>
+      <c r="D42" s="52"/>
+      <c r="E42" s="53"/>
+      <c r="F42" s="53"/>
+      <c r="G42" s="54"/>
+      <c r="H42" s="12"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="19">
         <v>36</v>
       </c>
-      <c r="B43" s="3"/>
-      <c r="C43" s="12"/>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="26"/>
-      <c r="G43" s="21"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="29">
+      <c r="B43" s="47"/>
+      <c r="C43" s="48"/>
+      <c r="D43" s="52"/>
+      <c r="E43" s="53"/>
+      <c r="F43" s="53"/>
+      <c r="G43" s="54"/>
+      <c r="H43" s="12"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="19">
         <v>37</v>
       </c>
-      <c r="B44" s="3"/>
-      <c r="C44" s="12"/>
-      <c r="D44" s="13"/>
-      <c r="E44" s="13"/>
-      <c r="F44" s="26"/>
-      <c r="G44" s="21"/>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="29">
+      <c r="B44" s="47"/>
+      <c r="C44" s="48"/>
+      <c r="D44" s="52"/>
+      <c r="E44" s="53"/>
+      <c r="F44" s="53"/>
+      <c r="G44" s="54"/>
+      <c r="H44" s="12"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="19">
         <v>38</v>
       </c>
-      <c r="B45" s="3"/>
-      <c r="C45" s="15"/>
-      <c r="D45" s="16"/>
-      <c r="E45" s="16"/>
-      <c r="F45" s="27"/>
-      <c r="G45" s="22"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="29">
+      <c r="B45" s="47"/>
+      <c r="C45" s="46"/>
+      <c r="D45" s="55"/>
+      <c r="E45" s="56"/>
+      <c r="F45" s="56"/>
+      <c r="G45" s="57"/>
+      <c r="H45" s="13"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="19">
         <v>39</v>
       </c>
-      <c r="B46" s="3"/>
-      <c r="C46" s="12"/>
-      <c r="D46" s="13"/>
-      <c r="E46" s="13"/>
-      <c r="F46" s="26"/>
-      <c r="G46" s="21"/>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="29">
+      <c r="B46" s="47"/>
+      <c r="C46" s="48"/>
+      <c r="D46" s="52"/>
+      <c r="E46" s="53"/>
+      <c r="F46" s="53"/>
+      <c r="G46" s="54"/>
+      <c r="H46" s="12"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="19">
         <v>40</v>
       </c>
-      <c r="B47" s="3"/>
-      <c r="C47" s="12"/>
-      <c r="D47" s="13"/>
-      <c r="E47" s="13"/>
-      <c r="F47" s="26"/>
-      <c r="G47" s="21"/>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="29">
+      <c r="B47" s="47"/>
+      <c r="C47" s="48"/>
+      <c r="D47" s="52"/>
+      <c r="E47" s="53"/>
+      <c r="F47" s="53"/>
+      <c r="G47" s="54"/>
+      <c r="H47" s="12"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="19">
         <v>41</v>
       </c>
-      <c r="B48" s="4"/>
-      <c r="C48" s="12"/>
-      <c r="D48" s="13"/>
-      <c r="E48" s="13"/>
-      <c r="F48" s="26"/>
-      <c r="G48" s="21"/>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="29">
+      <c r="B48" s="47"/>
+      <c r="C48" s="48"/>
+      <c r="D48" s="52"/>
+      <c r="E48" s="53"/>
+      <c r="F48" s="53"/>
+      <c r="G48" s="54"/>
+      <c r="H48" s="12"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="19">
         <v>42</v>
       </c>
-      <c r="B49" s="3"/>
-      <c r="C49" s="12"/>
-      <c r="D49" s="13"/>
-      <c r="E49" s="13"/>
-      <c r="F49" s="26"/>
-      <c r="G49" s="21"/>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="29">
+      <c r="B49" s="47"/>
+      <c r="C49" s="48"/>
+      <c r="D49" s="52"/>
+      <c r="E49" s="53"/>
+      <c r="F49" s="53"/>
+      <c r="G49" s="54"/>
+      <c r="H49" s="12"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="19">
         <v>43</v>
       </c>
-      <c r="B50" s="3"/>
-      <c r="C50" s="12"/>
-      <c r="D50" s="13"/>
-      <c r="E50" s="13"/>
-      <c r="F50" s="26"/>
-      <c r="G50" s="21"/>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="29">
+      <c r="B50" s="47"/>
+      <c r="C50" s="48"/>
+      <c r="D50" s="52"/>
+      <c r="E50" s="53"/>
+      <c r="F50" s="53"/>
+      <c r="G50" s="54"/>
+      <c r="H50" s="12"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="19">
         <v>44</v>
       </c>
-      <c r="B51" s="3"/>
-      <c r="C51" s="15"/>
-      <c r="D51" s="16"/>
-      <c r="E51" s="16"/>
-      <c r="F51" s="27"/>
-      <c r="G51" s="22"/>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="29">
+      <c r="B51" s="47"/>
+      <c r="C51" s="46"/>
+      <c r="D51" s="55"/>
+      <c r="E51" s="56"/>
+      <c r="F51" s="56"/>
+      <c r="G51" s="57"/>
+      <c r="H51" s="13"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="19">
         <v>45</v>
       </c>
-      <c r="B52" s="3"/>
-      <c r="C52" s="12"/>
-      <c r="D52" s="13"/>
-      <c r="E52" s="13"/>
-      <c r="F52" s="26"/>
-      <c r="G52" s="21"/>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="29">
+      <c r="B52" s="47"/>
+      <c r="C52" s="48"/>
+      <c r="D52" s="52"/>
+      <c r="E52" s="53"/>
+      <c r="F52" s="53"/>
+      <c r="G52" s="54"/>
+      <c r="H52" s="12"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="19">
         <v>46</v>
       </c>
-      <c r="B53" s="3"/>
-      <c r="C53" s="12"/>
-      <c r="D53" s="13"/>
-      <c r="E53" s="13"/>
-      <c r="F53" s="26"/>
-      <c r="G53" s="21"/>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="29">
+      <c r="B53" s="47"/>
+      <c r="C53" s="48"/>
+      <c r="D53" s="52"/>
+      <c r="E53" s="53"/>
+      <c r="F53" s="53"/>
+      <c r="G53" s="54"/>
+      <c r="H53" s="12"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="19">
         <v>47</v>
       </c>
-      <c r="B54" s="3"/>
-      <c r="C54" s="12"/>
-      <c r="D54" s="13"/>
-      <c r="E54" s="13"/>
-      <c r="F54" s="26"/>
-      <c r="G54" s="21"/>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="29">
+      <c r="B54" s="47"/>
+      <c r="C54" s="48"/>
+      <c r="D54" s="52"/>
+      <c r="E54" s="53"/>
+      <c r="F54" s="53"/>
+      <c r="G54" s="54"/>
+      <c r="H54" s="12"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="19">
         <v>48</v>
       </c>
-      <c r="B55" s="3"/>
-      <c r="C55" s="12"/>
-      <c r="D55" s="13"/>
-      <c r="E55" s="13"/>
-      <c r="F55" s="26"/>
-      <c r="G55" s="21"/>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="29">
+      <c r="B55" s="47"/>
+      <c r="C55" s="48"/>
+      <c r="D55" s="52"/>
+      <c r="E55" s="53"/>
+      <c r="F55" s="53"/>
+      <c r="G55" s="54"/>
+      <c r="H55" s="12"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="19">
         <v>49</v>
       </c>
-      <c r="B56" s="3"/>
-      <c r="C56" s="15"/>
-      <c r="D56" s="16"/>
-      <c r="E56" s="16"/>
-      <c r="F56" s="27"/>
-      <c r="G56" s="22"/>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="29">
+      <c r="B56" s="47"/>
+      <c r="C56" s="46"/>
+      <c r="D56" s="55"/>
+      <c r="E56" s="56"/>
+      <c r="F56" s="56"/>
+      <c r="G56" s="57"/>
+      <c r="H56" s="13"/>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="19">
         <v>50</v>
       </c>
-      <c r="B57" s="3"/>
-      <c r="C57" s="12"/>
-      <c r="D57" s="13"/>
-      <c r="E57" s="13"/>
-      <c r="F57" s="26"/>
-      <c r="G57" s="21"/>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="29">
+      <c r="B57" s="47"/>
+      <c r="C57" s="48"/>
+      <c r="D57" s="52"/>
+      <c r="E57" s="53"/>
+      <c r="F57" s="53"/>
+      <c r="G57" s="54"/>
+      <c r="H57" s="12"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="19">
         <v>51</v>
       </c>
-      <c r="B58" s="4"/>
-      <c r="C58" s="12"/>
-      <c r="D58" s="13"/>
-      <c r="E58" s="13"/>
-      <c r="F58" s="26"/>
-      <c r="G58" s="21"/>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="29">
+      <c r="B58" s="47"/>
+      <c r="C58" s="48"/>
+      <c r="D58" s="52"/>
+      <c r="E58" s="53"/>
+      <c r="F58" s="53"/>
+      <c r="G58" s="54"/>
+      <c r="H58" s="12"/>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="19">
         <v>52</v>
       </c>
-      <c r="B59" s="3"/>
-      <c r="C59" s="12"/>
-      <c r="D59" s="13"/>
-      <c r="E59" s="13"/>
-      <c r="F59" s="26"/>
-      <c r="G59" s="21"/>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="29">
+      <c r="B59" s="47"/>
+      <c r="C59" s="48"/>
+      <c r="D59" s="52"/>
+      <c r="E59" s="53"/>
+      <c r="F59" s="53"/>
+      <c r="G59" s="54"/>
+      <c r="H59" s="12"/>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="19">
         <v>53</v>
       </c>
-      <c r="B60" s="3"/>
-      <c r="C60" s="12"/>
-      <c r="D60" s="13"/>
-      <c r="E60" s="13"/>
-      <c r="F60" s="26"/>
-      <c r="G60" s="21"/>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="29">
+      <c r="B60" s="47"/>
+      <c r="C60" s="48"/>
+      <c r="D60" s="52"/>
+      <c r="E60" s="53"/>
+      <c r="F60" s="53"/>
+      <c r="G60" s="54"/>
+      <c r="H60" s="12"/>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="19">
         <v>54</v>
       </c>
-      <c r="B61" s="3"/>
-      <c r="C61" s="15"/>
-      <c r="D61" s="16"/>
-      <c r="E61" s="16"/>
-      <c r="F61" s="27"/>
-      <c r="G61" s="22"/>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="29">
+      <c r="B61" s="47"/>
+      <c r="C61" s="46"/>
+      <c r="D61" s="55"/>
+      <c r="E61" s="56"/>
+      <c r="F61" s="56"/>
+      <c r="G61" s="57"/>
+      <c r="H61" s="13"/>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" s="19">
         <v>55</v>
       </c>
-      <c r="B62" s="3"/>
-      <c r="C62" s="12"/>
-      <c r="D62" s="13"/>
-      <c r="E62" s="13"/>
-      <c r="F62" s="26"/>
-      <c r="G62" s="21"/>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="29">
+      <c r="B62" s="47"/>
+      <c r="C62" s="48"/>
+      <c r="D62" s="52"/>
+      <c r="E62" s="53"/>
+      <c r="F62" s="53"/>
+      <c r="G62" s="54"/>
+      <c r="H62" s="12"/>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="19">
         <v>56</v>
       </c>
-      <c r="B63" s="3"/>
-      <c r="C63" s="12"/>
-      <c r="D63" s="13"/>
-      <c r="E63" s="13"/>
-      <c r="F63" s="26"/>
-      <c r="G63" s="21"/>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="29">
+      <c r="B63" s="47"/>
+      <c r="C63" s="48"/>
+      <c r="D63" s="52"/>
+      <c r="E63" s="53"/>
+      <c r="F63" s="53"/>
+      <c r="G63" s="54"/>
+      <c r="H63" s="12"/>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" s="19">
         <v>57</v>
       </c>
-      <c r="B64" s="3"/>
-      <c r="C64" s="12"/>
-      <c r="D64" s="13"/>
-      <c r="E64" s="13"/>
-      <c r="F64" s="26"/>
-      <c r="G64" s="21"/>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="29">
+      <c r="B64" s="47"/>
+      <c r="C64" s="48"/>
+      <c r="D64" s="52"/>
+      <c r="E64" s="53"/>
+      <c r="F64" s="53"/>
+      <c r="G64" s="54"/>
+      <c r="H64" s="12"/>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="19">
         <v>58</v>
       </c>
-      <c r="B65" s="3"/>
-      <c r="C65" s="12"/>
-      <c r="D65" s="13"/>
-      <c r="E65" s="13"/>
-      <c r="F65" s="26"/>
-      <c r="G65" s="21"/>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="29">
+      <c r="B65" s="47"/>
+      <c r="C65" s="48"/>
+      <c r="D65" s="52"/>
+      <c r="E65" s="53"/>
+      <c r="F65" s="53"/>
+      <c r="G65" s="54"/>
+      <c r="H65" s="12"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="19">
         <v>59</v>
       </c>
-      <c r="B66" s="3"/>
-      <c r="C66" s="15"/>
-      <c r="D66" s="16"/>
-      <c r="E66" s="16"/>
-      <c r="F66" s="27"/>
-      <c r="G66" s="22"/>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A67" s="29">
+      <c r="B66" s="47"/>
+      <c r="C66" s="46"/>
+      <c r="D66" s="55"/>
+      <c r="E66" s="56"/>
+      <c r="F66" s="56"/>
+      <c r="G66" s="57"/>
+      <c r="H66" s="13"/>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="19">
         <v>60</v>
       </c>
-      <c r="B67" s="3"/>
-      <c r="C67" s="12"/>
-      <c r="D67" s="13"/>
-      <c r="E67" s="13"/>
-      <c r="F67" s="26"/>
-      <c r="G67" s="21"/>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="29">
+      <c r="B67" s="47"/>
+      <c r="C67" s="48"/>
+      <c r="D67" s="52"/>
+      <c r="E67" s="53"/>
+      <c r="F67" s="53"/>
+      <c r="G67" s="54"/>
+      <c r="H67" s="12"/>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" s="19">
         <v>61</v>
       </c>
-      <c r="B68" s="4"/>
-      <c r="C68" s="12"/>
-      <c r="D68" s="13"/>
-      <c r="E68" s="13"/>
-      <c r="F68" s="26"/>
-      <c r="G68" s="21"/>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="29">
+      <c r="B68" s="47"/>
+      <c r="C68" s="48"/>
+      <c r="D68" s="52"/>
+      <c r="E68" s="53"/>
+      <c r="F68" s="53"/>
+      <c r="G68" s="54"/>
+      <c r="H68" s="12"/>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" s="19">
         <v>62</v>
       </c>
-      <c r="B69" s="3"/>
-      <c r="C69" s="12"/>
-      <c r="D69" s="13"/>
-      <c r="E69" s="13"/>
-      <c r="F69" s="26"/>
-      <c r="G69" s="21"/>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="29">
+      <c r="B69" s="47"/>
+      <c r="C69" s="48"/>
+      <c r="D69" s="52"/>
+      <c r="E69" s="53"/>
+      <c r="F69" s="53"/>
+      <c r="G69" s="54"/>
+      <c r="H69" s="12"/>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="19">
         <v>63</v>
       </c>
-      <c r="B70" s="3"/>
-      <c r="C70" s="12"/>
-      <c r="D70" s="13"/>
-      <c r="E70" s="13"/>
-      <c r="F70" s="26"/>
-      <c r="G70" s="21"/>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="29">
+      <c r="B70" s="47"/>
+      <c r="C70" s="48"/>
+      <c r="D70" s="52"/>
+      <c r="E70" s="53"/>
+      <c r="F70" s="53"/>
+      <c r="G70" s="54"/>
+      <c r="H70" s="12"/>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="19">
         <v>64</v>
       </c>
-      <c r="B71" s="3"/>
-      <c r="C71" s="15"/>
-      <c r="D71" s="16"/>
-      <c r="E71" s="16"/>
-      <c r="F71" s="27"/>
-      <c r="G71" s="22"/>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="29">
+      <c r="B71" s="47"/>
+      <c r="C71" s="46"/>
+      <c r="D71" s="55"/>
+      <c r="E71" s="56"/>
+      <c r="F71" s="56"/>
+      <c r="G71" s="57"/>
+      <c r="H71" s="13"/>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="19">
         <v>65</v>
       </c>
-      <c r="B72" s="3"/>
-      <c r="C72" s="12"/>
-      <c r="D72" s="13"/>
-      <c r="E72" s="13"/>
-      <c r="F72" s="26"/>
-      <c r="G72" s="21"/>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="29">
+      <c r="B72" s="47"/>
+      <c r="C72" s="48"/>
+      <c r="D72" s="52"/>
+      <c r="E72" s="53"/>
+      <c r="F72" s="53"/>
+      <c r="G72" s="54"/>
+      <c r="H72" s="12"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="19">
         <v>66</v>
       </c>
-      <c r="B73" s="3"/>
-      <c r="C73" s="12"/>
-      <c r="D73" s="13"/>
-      <c r="E73" s="13"/>
-      <c r="F73" s="26"/>
-      <c r="G73" s="21"/>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="29">
+      <c r="B73" s="47"/>
+      <c r="C73" s="48"/>
+      <c r="D73" s="52"/>
+      <c r="E73" s="53"/>
+      <c r="F73" s="53"/>
+      <c r="G73" s="54"/>
+      <c r="H73" s="12"/>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="19">
         <v>67</v>
       </c>
-      <c r="B74" s="3"/>
-      <c r="C74" s="12"/>
-      <c r="D74" s="13"/>
-      <c r="E74" s="13"/>
-      <c r="F74" s="26"/>
-      <c r="G74" s="21"/>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="29">
+      <c r="B74" s="47"/>
+      <c r="C74" s="48"/>
+      <c r="D74" s="52"/>
+      <c r="E74" s="53"/>
+      <c r="F74" s="53"/>
+      <c r="G74" s="54"/>
+      <c r="H74" s="12"/>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" s="19">
         <v>68</v>
       </c>
-      <c r="B75" s="3"/>
-      <c r="C75" s="12"/>
-      <c r="D75" s="13"/>
-      <c r="E75" s="13"/>
-      <c r="F75" s="26"/>
-      <c r="G75" s="21"/>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="29">
+      <c r="B75" s="47"/>
+      <c r="C75" s="48"/>
+      <c r="D75" s="52"/>
+      <c r="E75" s="53"/>
+      <c r="F75" s="53"/>
+      <c r="G75" s="54"/>
+      <c r="H75" s="12"/>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" s="19">
         <v>69</v>
       </c>
-      <c r="B76" s="3"/>
-      <c r="C76" s="15"/>
-      <c r="D76" s="16"/>
-      <c r="E76" s="16"/>
-      <c r="F76" s="27"/>
-      <c r="G76" s="22"/>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="29">
+      <c r="B76" s="47"/>
+      <c r="C76" s="46"/>
+      <c r="D76" s="55"/>
+      <c r="E76" s="56"/>
+      <c r="F76" s="56"/>
+      <c r="G76" s="57"/>
+      <c r="H76" s="13"/>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" s="19">
         <v>70</v>
       </c>
-      <c r="B77" s="3"/>
-      <c r="C77" s="12"/>
-      <c r="D77" s="13"/>
-      <c r="E77" s="13"/>
-      <c r="F77" s="26"/>
-      <c r="G77" s="21"/>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="29">
+      <c r="B77" s="47"/>
+      <c r="C77" s="48"/>
+      <c r="D77" s="52"/>
+      <c r="E77" s="53"/>
+      <c r="F77" s="53"/>
+      <c r="G77" s="54"/>
+      <c r="H77" s="12"/>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" s="19">
         <v>71</v>
       </c>
-      <c r="B78" s="3"/>
-      <c r="C78" s="12"/>
-      <c r="D78" s="13"/>
-      <c r="E78" s="13"/>
-      <c r="F78" s="26"/>
-      <c r="G78" s="21"/>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="29">
+      <c r="B78" s="47"/>
+      <c r="C78" s="48"/>
+      <c r="D78" s="52"/>
+      <c r="E78" s="53"/>
+      <c r="F78" s="53"/>
+      <c r="G78" s="54"/>
+      <c r="H78" s="12"/>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" s="19">
         <v>72</v>
       </c>
-      <c r="B79" s="4"/>
-      <c r="C79" s="12"/>
-      <c r="D79" s="13"/>
-      <c r="E79" s="13"/>
-      <c r="F79" s="26"/>
-      <c r="G79" s="21"/>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="29">
+      <c r="B79" s="47"/>
+      <c r="C79" s="48"/>
+      <c r="D79" s="52"/>
+      <c r="E79" s="53"/>
+      <c r="F79" s="53"/>
+      <c r="G79" s="54"/>
+      <c r="H79" s="12"/>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" s="19">
         <v>73</v>
       </c>
-      <c r="B80" s="3"/>
-      <c r="C80" s="12"/>
-      <c r="D80" s="13"/>
-      <c r="E80" s="13"/>
-      <c r="F80" s="26"/>
-      <c r="G80" s="21"/>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A81" s="29">
+      <c r="B80" s="47"/>
+      <c r="C80" s="48"/>
+      <c r="D80" s="52"/>
+      <c r="E80" s="53"/>
+      <c r="F80" s="53"/>
+      <c r="G80" s="54"/>
+      <c r="H80" s="12"/>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" s="19">
         <v>74</v>
       </c>
-      <c r="B81" s="3"/>
-      <c r="C81" s="15"/>
-      <c r="D81" s="16"/>
-      <c r="E81" s="16"/>
-      <c r="F81" s="27"/>
-      <c r="G81" s="22"/>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="29">
+      <c r="B81" s="47"/>
+      <c r="C81" s="46"/>
+      <c r="D81" s="55"/>
+      <c r="E81" s="56"/>
+      <c r="F81" s="56"/>
+      <c r="G81" s="57"/>
+      <c r="H81" s="13"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" s="19">
         <v>75</v>
       </c>
-      <c r="B82" s="3"/>
-      <c r="C82" s="12"/>
-      <c r="D82" s="13"/>
-      <c r="E82" s="13"/>
-      <c r="F82" s="26"/>
-      <c r="G82" s="21"/>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="29">
+      <c r="B82" s="47"/>
+      <c r="C82" s="48"/>
+      <c r="D82" s="52"/>
+      <c r="E82" s="53"/>
+      <c r="F82" s="53"/>
+      <c r="G82" s="54"/>
+      <c r="H82" s="12"/>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" s="19">
         <v>76</v>
       </c>
-      <c r="B83" s="3"/>
-      <c r="C83" s="12"/>
-      <c r="D83" s="13"/>
-      <c r="E83" s="13"/>
-      <c r="F83" s="26"/>
-      <c r="G83" s="21"/>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="29">
+      <c r="B83" s="47"/>
+      <c r="C83" s="48"/>
+      <c r="D83" s="52"/>
+      <c r="E83" s="53"/>
+      <c r="F83" s="53"/>
+      <c r="G83" s="54"/>
+      <c r="H83" s="12"/>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" s="19">
         <v>77</v>
       </c>
-      <c r="B84" s="3"/>
-      <c r="C84" s="12"/>
-      <c r="D84" s="13"/>
-      <c r="E84" s="13"/>
-      <c r="F84" s="26"/>
-      <c r="G84" s="21"/>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="29">
+      <c r="B84" s="47"/>
+      <c r="C84" s="48"/>
+      <c r="D84" s="52"/>
+      <c r="E84" s="53"/>
+      <c r="F84" s="53"/>
+      <c r="G84" s="54"/>
+      <c r="H84" s="12"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" s="19">
         <v>78</v>
       </c>
-      <c r="B85" s="3"/>
-      <c r="C85" s="12"/>
-      <c r="D85" s="13"/>
-      <c r="E85" s="13"/>
-      <c r="F85" s="26"/>
-      <c r="G85" s="21"/>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="29">
+      <c r="B85" s="47"/>
+      <c r="C85" s="48"/>
+      <c r="D85" s="52"/>
+      <c r="E85" s="53"/>
+      <c r="F85" s="53"/>
+      <c r="G85" s="54"/>
+      <c r="H85" s="12"/>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" s="19">
         <v>79</v>
       </c>
-      <c r="B86" s="3"/>
-      <c r="C86" s="15"/>
-      <c r="D86" s="16"/>
-      <c r="E86" s="16"/>
-      <c r="F86" s="27"/>
-      <c r="G86" s="22"/>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="29">
+      <c r="B86" s="47"/>
+      <c r="C86" s="46"/>
+      <c r="D86" s="55"/>
+      <c r="E86" s="56"/>
+      <c r="F86" s="56"/>
+      <c r="G86" s="57"/>
+      <c r="H86" s="13"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" s="19">
         <v>80</v>
       </c>
-      <c r="B87" s="3"/>
-      <c r="C87" s="12"/>
-      <c r="D87" s="13"/>
-      <c r="E87" s="13"/>
-      <c r="F87" s="26"/>
-      <c r="G87" s="21"/>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="29">
+      <c r="B87" s="47"/>
+      <c r="C87" s="48"/>
+      <c r="D87" s="52"/>
+      <c r="E87" s="53"/>
+      <c r="F87" s="53"/>
+      <c r="G87" s="54"/>
+      <c r="H87" s="12"/>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" s="19">
         <v>81</v>
       </c>
-      <c r="B88" s="3"/>
-      <c r="C88" s="12"/>
-      <c r="D88" s="13"/>
-      <c r="E88" s="13"/>
-      <c r="F88" s="26"/>
-      <c r="G88" s="21"/>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="29">
+      <c r="B88" s="47"/>
+      <c r="C88" s="48"/>
+      <c r="D88" s="52"/>
+      <c r="E88" s="53"/>
+      <c r="F88" s="53"/>
+      <c r="G88" s="54"/>
+      <c r="H88" s="12"/>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" s="19">
         <v>82</v>
       </c>
-      <c r="B89" s="3"/>
-      <c r="C89" s="12"/>
-      <c r="D89" s="13"/>
-      <c r="E89" s="13"/>
-      <c r="F89" s="26"/>
-      <c r="G89" s="21"/>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="29">
+      <c r="B89" s="47"/>
+      <c r="C89" s="48"/>
+      <c r="D89" s="52"/>
+      <c r="E89" s="53"/>
+      <c r="F89" s="53"/>
+      <c r="G89" s="54"/>
+      <c r="H89" s="12"/>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" s="19">
         <v>83</v>
       </c>
-      <c r="B90" s="4"/>
-      <c r="C90" s="12"/>
-      <c r="D90" s="13"/>
-      <c r="E90" s="13"/>
-      <c r="F90" s="26"/>
-      <c r="G90" s="21"/>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="29">
+      <c r="B90" s="47"/>
+      <c r="C90" s="48"/>
+      <c r="D90" s="52"/>
+      <c r="E90" s="53"/>
+      <c r="F90" s="53"/>
+      <c r="G90" s="54"/>
+      <c r="H90" s="12"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" s="19">
         <v>84</v>
       </c>
-      <c r="B91" s="3"/>
-      <c r="C91" s="12"/>
-      <c r="D91" s="13"/>
-      <c r="E91" s="13"/>
-      <c r="F91" s="26"/>
-      <c r="G91" s="21"/>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="29">
+      <c r="B91" s="47"/>
+      <c r="C91" s="48"/>
+      <c r="D91" s="52"/>
+      <c r="E91" s="53"/>
+      <c r="F91" s="53"/>
+      <c r="G91" s="54"/>
+      <c r="H91" s="12"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" s="19">
         <v>85</v>
       </c>
-      <c r="B92" s="3"/>
-      <c r="C92" s="15"/>
-      <c r="D92" s="16"/>
-      <c r="E92" s="16"/>
-      <c r="F92" s="27"/>
-      <c r="G92" s="22"/>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="29">
+      <c r="B92" s="47"/>
+      <c r="C92" s="46"/>
+      <c r="D92" s="55"/>
+      <c r="E92" s="56"/>
+      <c r="F92" s="56"/>
+      <c r="G92" s="57"/>
+      <c r="H92" s="13"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" s="19">
         <v>86</v>
       </c>
-      <c r="B93" s="3"/>
-      <c r="C93" s="12"/>
-      <c r="D93" s="13"/>
-      <c r="E93" s="13"/>
-      <c r="F93" s="26"/>
-      <c r="G93" s="21"/>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="29">
+      <c r="B93" s="47"/>
+      <c r="C93" s="48"/>
+      <c r="D93" s="52"/>
+      <c r="E93" s="53"/>
+      <c r="F93" s="53"/>
+      <c r="G93" s="54"/>
+      <c r="H93" s="12"/>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" s="19">
         <v>87</v>
       </c>
-      <c r="B94" s="3"/>
-      <c r="C94" s="12"/>
-      <c r="D94" s="13"/>
-      <c r="E94" s="13"/>
-      <c r="F94" s="26"/>
-      <c r="G94" s="21"/>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="29">
+      <c r="B94" s="47"/>
+      <c r="C94" s="48"/>
+      <c r="D94" s="52"/>
+      <c r="E94" s="53"/>
+      <c r="F94" s="53"/>
+      <c r="G94" s="54"/>
+      <c r="H94" s="12"/>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" s="19">
         <v>88</v>
       </c>
-      <c r="B95" s="3"/>
-      <c r="C95" s="12"/>
-      <c r="D95" s="13"/>
-      <c r="E95" s="13"/>
-      <c r="F95" s="26"/>
-      <c r="G95" s="21"/>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="29">
+      <c r="B95" s="47"/>
+      <c r="C95" s="48"/>
+      <c r="D95" s="52"/>
+      <c r="E95" s="53"/>
+      <c r="F95" s="53"/>
+      <c r="G95" s="54"/>
+      <c r="H95" s="12"/>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" s="19">
         <v>89</v>
       </c>
-      <c r="B96" s="3"/>
-      <c r="C96" s="12"/>
-      <c r="D96" s="13"/>
-      <c r="E96" s="13"/>
-      <c r="F96" s="26"/>
-      <c r="G96" s="21"/>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="8">
+      <c r="B96" s="47"/>
+      <c r="C96" s="48"/>
+      <c r="D96" s="52"/>
+      <c r="E96" s="53"/>
+      <c r="F96" s="53"/>
+      <c r="G96" s="54"/>
+      <c r="H96" s="12"/>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" s="2">
         <v>90</v>
       </c>
-      <c r="B97" s="5"/>
-      <c r="C97" s="9"/>
-      <c r="D97" s="10"/>
-      <c r="E97" s="10"/>
-      <c r="F97" s="25"/>
-      <c r="G97" s="23"/>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="31" t="s">
+      <c r="B97" s="49"/>
+      <c r="C97" s="50"/>
+      <c r="D97" s="58"/>
+      <c r="E97" s="59"/>
+      <c r="F97" s="59"/>
+      <c r="G97" s="60"/>
+      <c r="H97" s="14"/>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="B98" s="32"/>
-      <c r="C98" s="17" t="str">
-        <f>IF(SUM(C8:C97)=0,"",AVERAGE(C8:C97))</f>
-        <v/>
-      </c>
-      <c r="D98" s="18" t="str">
+      <c r="B98" s="35"/>
+      <c r="C98" s="42"/>
+      <c r="D98" s="9" t="str">
         <f>IF(SUM(D8:D97)=0,"",AVERAGE(D8:D97))</f>
         <v/>
       </c>
-      <c r="E98" s="18" t="str">
+      <c r="E98" s="10" t="str">
         <f>IF(SUM(E8:E97)=0,"",AVERAGE(E8:E97))</f>
         <v/>
       </c>
-      <c r="F98" s="28"/>
-      <c r="G98" s="19" t="str">
-        <f>IF(SUM(G8:G97)=0,"",AVERAGE(G8:G97))</f>
+      <c r="F98" s="10" t="str">
+        <f>IF(SUM(F8:F97)=0,"",AVERAGE(F8:F97))</f>
         <v/>
       </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="33" t="s">
+      <c r="G98" s="17"/>
+      <c r="H98" s="11" t="str">
+        <f>IF(SUM(H8:H97)=0,"",AVERAGE(H8:H97))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="B99" s="34"/>
-      <c r="C99" s="12" t="str">
-        <f>IF(SUM(C8:C97)=0,"",MEDIAN(C8:C97))</f>
-        <v/>
-      </c>
-      <c r="D99" s="13" t="str">
+      <c r="B99" s="37"/>
+      <c r="C99" s="43"/>
+      <c r="D99" s="6" t="str">
         <f>IF(SUM(D8:D97)=0,"",MEDIAN(D8:D97))</f>
         <v/>
       </c>
-      <c r="E99" s="13" t="str">
+      <c r="E99" s="7" t="str">
         <f>IF(SUM(E8:E97)=0,"",MEDIAN(E8:E97))</f>
         <v/>
       </c>
-      <c r="F99" s="26"/>
-      <c r="G99" s="14" t="str">
-        <f>IF(SUM(G8:G97)=0,"",MEDIAN(G8:G97))</f>
+      <c r="F99" s="7" t="str">
+        <f>IF(SUM(F8:F97)=0,"",MEDIAN(F8:F97))</f>
         <v/>
       </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="33" t="s">
+      <c r="G99" s="16"/>
+      <c r="H99" s="8" t="str">
+        <f>IF(SUM(H8:H97)=0,"",MEDIAN(H8:H97))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="B100" s="34"/>
-      <c r="C100" s="12" t="str">
-        <f>IF(SUM(C8:C97)=0,"",MAX(C8:C97))</f>
-        <v/>
-      </c>
-      <c r="D100" s="13" t="str">
+      <c r="B100" s="37"/>
+      <c r="C100" s="43"/>
+      <c r="D100" s="6" t="str">
         <f>IF(SUM(D8:D97)=0,"",MAX(D8:D97))</f>
         <v/>
       </c>
-      <c r="E100" s="13" t="str">
+      <c r="E100" s="7" t="str">
         <f>IF(SUM(E8:E97)=0,"",MAX(E8:E97))</f>
         <v/>
       </c>
-      <c r="F100" s="26"/>
-      <c r="G100" s="14" t="str">
-        <f>IF(SUM(G8:G97)=0,"",MAX(G8:G97))</f>
+      <c r="F100" s="7" t="str">
+        <f>IF(SUM(F8:F97)=0,"",MAX(F8:F97))</f>
         <v/>
       </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="37" t="s">
+      <c r="G100" s="16"/>
+      <c r="H100" s="8" t="str">
+        <f>IF(SUM(H8:H97)=0,"",MAX(H8:H97))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="B101" s="38"/>
-      <c r="C101" s="9" t="str">
-        <f>IF(SUM(C8:C97)=0,"",MIN(C8:C97))</f>
-        <v/>
-      </c>
-      <c r="D101" s="10" t="str">
+      <c r="B101" s="41"/>
+      <c r="C101" s="44"/>
+      <c r="D101" s="3" t="str">
         <f>IF(SUM(D8:D97)=0,"",MIN(D8:D97))</f>
         <v/>
       </c>
-      <c r="E101" s="10" t="str">
+      <c r="E101" s="4" t="str">
         <f>IF(SUM(E8:E97)=0,"",MIN(E8:E97))</f>
         <v/>
       </c>
-      <c r="F101" s="25"/>
-      <c r="G101" s="11" t="str">
-        <f>IF(SUM(G8:G97)=0,"",MIN(G8:G97))</f>
+      <c r="F101" s="4" t="str">
+        <f>IF(SUM(F8:F97)=0,"",MIN(F8:F97))</f>
         <v/>
       </c>
-    </row>
-    <row r="102" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="35" t="s">
+      <c r="G101" s="15"/>
+      <c r="H101" s="5" t="str">
+        <f>IF(SUM(H8:H97)=0,"",MIN(H8:H97))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="B102" s="36"/>
-      <c r="C102" s="36"/>
-      <c r="D102" s="36"/>
-      <c r="E102" s="36"/>
-      <c r="F102" s="24"/>
+      <c r="B102" s="39"/>
+      <c r="C102" s="39"/>
+      <c r="D102" s="39"/>
+      <c r="E102" s="39"/>
+      <c r="F102" s="39"/>
       <c r="G102" s="20"/>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="30" t="s">
+      <c r="H102" s="51">
+        <f ca="1">NOW()</f>
+        <v>46263.403120138886</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="B103" s="30"/>
-      <c r="C103" s="30"/>
-      <c r="D103" s="30"/>
-      <c r="E103" s="30"/>
-      <c r="F103" s="30"/>
-      <c r="G103" s="30"/>
+      <c r="B103" s="33"/>
+      <c r="C103" s="33"/>
+      <c r="D103" s="33"/>
+      <c r="E103" s="33"/>
+      <c r="F103" s="33"/>
+      <c r="G103" s="33"/>
+      <c r="H103" s="33"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="C6:G6"/>
+  <mergeCells count="14">
+    <mergeCell ref="A103:H103"/>
+    <mergeCell ref="A98:B98"/>
+    <mergeCell ref="A99:B99"/>
+    <mergeCell ref="A102:F102"/>
+    <mergeCell ref="A100:B100"/>
+    <mergeCell ref="A101:B101"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="D6:H6"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="B6:B7"/>
-    <mergeCell ref="A103:G103"/>
-    <mergeCell ref="A98:B98"/>
-    <mergeCell ref="A99:B99"/>
-    <mergeCell ref="A102:E102"/>
-    <mergeCell ref="A100:B100"/>
-    <mergeCell ref="A101:B101"/>
+    <mergeCell ref="C6:C7"/>
   </mergeCells>
   <pageMargins left="0.59055118110236227" right="0.43307086614173229" top="0.43307086614173229" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup scale="92" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>